--- a/DATA_ALTERNATIF.xlsx
+++ b/DATA_ALTERNATIF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\arinda nitip bess\KULIAH\TUGAS AKHIEEERRRRR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D5E2276-E18C-4399-942A-1F6497DD09FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01F48F8-90DB-4B7F-A2A1-5B43959F76D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12096" xr2:uid="{4B482624-5510-4144-BE40-63FAEEB392F9}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="15120" windowHeight="8604" xr2:uid="{4B482624-5510-4144-BE40-63FAEEB392F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
-  <si>
-    <t>DAFTAR ALTERNATIF</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>No</t>
   </si>
@@ -509,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E989D85B-6182-4F04-9D27-9762BC3F92F4}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.44140625" customWidth="1"/>
@@ -522,152 +519,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3">
-        <v>3</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>3</v>
-      </c>
-      <c r="H6" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
@@ -682,73 +700,73 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D10" s="3">
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -757,21 +775,21 @@
         <v>2</v>
       </c>
       <c r="H10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -786,15 +804,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -803,30 +821,30 @@
         <v>1</v>
       </c>
       <c r="F12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="D13" s="3">
         <v>3</v>
       </c>
       <c r="E13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="3">
         <v>2</v>
@@ -835,32 +853,6 @@
         <v>3</v>
       </c>
       <c r="H13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
         <v>2</v>
       </c>
     </row>

--- a/DATA_ALTERNATIF.xlsx
+++ b/DATA_ALTERNATIF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01F48F8-90DB-4B7F-A2A1-5B43959F76D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF48AF1-181E-49FE-A919-1D9BA536C381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="15120" windowHeight="8604" xr2:uid="{4B482624-5510-4144-BE40-63FAEEB392F9}"/>
+    <workbookView xWindow="5904" yWindow="480" windowWidth="15120" windowHeight="8604" xr2:uid="{4B482624-5510-4144-BE40-63FAEEB392F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,24 +42,6 @@
     <t xml:space="preserve">Nama </t>
   </si>
   <si>
-    <t xml:space="preserve">Jurusan </t>
-  </si>
-  <si>
-    <t>Penghasilan ortu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumlah Tanggungan </t>
-  </si>
-  <si>
-    <t>Status Keluarga</t>
-  </si>
-  <si>
-    <t>Prestasi akademik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motivasi belajar </t>
-  </si>
-  <si>
     <t>Rico saputra</t>
   </si>
   <si>
@@ -115,6 +97,24 @@
   </si>
   <si>
     <t>Nur Hidayat Sholikah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kelas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penghasilan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanggungan </t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Akademik</t>
+  </si>
+  <si>
+    <t>Motivasi</t>
   </si>
 </sst>
 </file>
@@ -526,22 +526,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -549,10 +549,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -575,10 +575,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -601,10 +601,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -627,10 +627,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -653,10 +653,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -679,10 +679,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -705,10 +705,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
@@ -731,10 +731,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -757,10 +757,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -783,10 +783,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -809,10 +809,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -835,10 +835,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
